--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_life.xlsx
@@ -588,115 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0722</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>0.008489999999999999</v>
+        <v>0.0312</v>
       </c>
       <c r="G2">
-        <v>0.0625083300013328</v>
+        <v>0.04614392643884388</v>
       </c>
       <c r="H2">
-        <v>0.0625083300013328</v>
+        <v>0.04614392643884388</v>
       </c>
       <c r="I2">
-        <v>0.05964280954284952</v>
+        <v>0.05113397437694486</v>
       </c>
       <c r="J2">
-        <v>0.05606932004165081</v>
+        <v>0.04886188853165119</v>
       </c>
       <c r="K2">
-        <v>139.9</v>
+        <v>152.2</v>
       </c>
       <c r="L2">
-        <v>0.04661468745834999</v>
+        <v>0.0426677132684814</v>
       </c>
       <c r="M2">
-        <v>108.8</v>
+        <v>157.2</v>
       </c>
       <c r="N2">
-        <v>0.02418852823477101</v>
+        <v>0.02698527139767226</v>
       </c>
       <c r="O2">
-        <v>0.7776983559685489</v>
+        <v>1.032851511169514</v>
       </c>
       <c r="P2">
-        <v>108.8</v>
+        <v>143.7</v>
       </c>
       <c r="Q2">
-        <v>0.02418852823477101</v>
+        <v>0.02466783396848285</v>
       </c>
       <c r="R2">
-        <v>0.7776983559685489</v>
+        <v>0.9441524310118266</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.08587786259541985</v>
       </c>
       <c r="U2">
-        <v>191.7</v>
+        <v>293.3</v>
       </c>
       <c r="V2">
-        <v>0.04261894175188973</v>
+        <v>0.05034847392453737</v>
       </c>
       <c r="W2">
-        <v>-0.3179122182680902</v>
+        <v>-0.3421487603305785</v>
       </c>
       <c r="X2">
-        <v>0.06210668035617091</v>
+        <v>0.09643605904432476</v>
       </c>
       <c r="Y2">
-        <v>-0.3800188986242611</v>
+        <v>-0.4385848193749032</v>
       </c>
       <c r="Z2">
-        <v>3.315565326424986</v>
-      </c>
-      <c r="AA2">
-        <v>0.2015017370839404</v>
+        <v>3.437174792830989</v>
       </c>
       <c r="AB2">
-        <v>0.06192106042955024</v>
-      </c>
-      <c r="AC2">
-        <v>0.1395837172222133</v>
+        <v>0.09604425019732928</v>
       </c>
       <c r="AD2">
-        <v>33.7</v>
+        <v>51.003</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>33.7</v>
+        <v>51.003</v>
       </c>
       <c r="AG2">
-        <v>-158</v>
+        <v>-242.297</v>
       </c>
       <c r="AH2">
-        <v>0.007436502857647242</v>
+        <v>0.008679289014044815</v>
       </c>
       <c r="AI2">
-        <v>0.02728965908170702</v>
+        <v>0.04246452963308641</v>
       </c>
       <c r="AJ2">
-        <v>-0.03640552995391705</v>
+        <v>-0.04339826795242717</v>
       </c>
       <c r="AK2">
-        <v>-0.1514570552147239</v>
+        <v>-0.2669136447107371</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AN2">
-        <v>0.1834512792596625</v>
+        <v>0.2724519230769231</v>
+      </c>
+      <c r="AO2">
+        <v>3880.851063829788</v>
       </c>
       <c r="AP2">
-        <v>-0.8600979858464889</v>
+        <v>-1.294321581196581</v>
+      </c>
+      <c r="AQ2">
+        <v>3880.851063829788</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Sagr Cooperative Insurance Company (SASE:8180)</t>
+          <t>Bupa Arabia for Cooperative Insurance Company (SASE:8210)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,97 +716,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.118</v>
+        <v>0.101</v>
+      </c>
+      <c r="E3">
+        <v>0.0312</v>
       </c>
       <c r="G3">
-        <v>-0.2980769230769231</v>
+        <v>0.05862394524104561</v>
       </c>
       <c r="H3">
-        <v>-0.2980769230769231</v>
+        <v>0.05862394524104561</v>
       </c>
       <c r="I3">
-        <v>-0.280982905982906</v>
+        <v>0.06263645482976338</v>
       </c>
       <c r="J3">
-        <v>-0.280982905982906</v>
+        <v>0.05428689443559332</v>
       </c>
       <c r="K3">
-        <v>-26.8</v>
+        <v>184</v>
       </c>
       <c r="L3">
-        <v>-0.2863247863247864</v>
+        <v>0.05428689443559332</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>157.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02749164932407618</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.8543478260869565</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>143.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02513072524090169</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.7809782608695651</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>13.5</v>
+      </c>
+      <c r="T3">
+        <v>0.08587786259541985</v>
       </c>
       <c r="U3">
-        <v>65.40000000000001</v>
+        <v>197.5</v>
       </c>
       <c r="V3">
-        <v>0.344391785150079</v>
+        <v>0.03453944492051556</v>
       </c>
       <c r="W3">
-        <v>-0.3179122182680902</v>
+        <v>0.1642563827887877</v>
       </c>
       <c r="X3">
-        <v>0.06192585645353457</v>
+        <v>0.09643605904432476</v>
       </c>
       <c r="Y3">
-        <v>-0.3798380747216248</v>
+        <v>0.06782032374446295</v>
       </c>
       <c r="Z3">
-        <v>-13.97014925373133</v>
+        <v>3.265947195991521</v>
       </c>
       <c r="AA3">
-        <v>3.925373134328355</v>
+        <v>0.1772981306610137</v>
       </c>
       <c r="AB3">
-        <v>0.06192585645353457</v>
+        <v>0.09606771152303745</v>
       </c>
       <c r="AC3">
-        <v>3.86344727787482</v>
+        <v>0.08123041913797624</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG3">
-        <v>-65.40000000000001</v>
+        <v>-147.5</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.008668365666337267</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.04325633705337831</v>
       </c>
       <c r="AJ3">
-        <v>-0.5253012048192771</v>
+        <v>-0.0264782967723405</v>
       </c>
       <c r="AK3">
-        <v>13.34693877551019</v>
+        <v>-0.1539023372287145</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0.2308402585410896</v>
       </c>
       <c r="AP3">
-        <v>2.515384615384616</v>
+        <v>-0.6809787626962143</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bupa Arabia for Cooperative Insurance Company (SASE:8210)</t>
+          <t>Al Sagr Cooperative Insurance Company (SASE:8180)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,115 +844,106 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0722</v>
-      </c>
-      <c r="E4">
-        <v>0.008489999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="G4">
-        <v>0.07807807807807807</v>
+        <v>-0.161590524534687</v>
       </c>
       <c r="H4">
-        <v>0.07807807807807807</v>
+        <v>-0.161590524534687</v>
       </c>
       <c r="I4">
-        <v>0.07654165793700676</v>
+        <v>-0.1641285956006768</v>
       </c>
       <c r="J4">
-        <v>0.06278371394650463</v>
+        <v>-0.1641285956006768</v>
       </c>
       <c r="K4">
-        <v>179.8</v>
+        <v>-20.7</v>
       </c>
       <c r="L4">
-        <v>0.06278371394650464</v>
+        <v>-0.1751269035532995</v>
       </c>
       <c r="M4">
-        <v>108.8</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02600506716382236</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6051167964404893</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>108.8</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02600506716382236</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6051167964404893</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>89.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V4">
-        <v>0.02136813423203786</v>
+        <v>1.374760994263863</v>
       </c>
       <c r="W4">
-        <v>0.1774050320670942</v>
+        <v>-0.3421487603305785</v>
       </c>
       <c r="X4">
-        <v>0.06222222546708436</v>
+        <v>0.09664239662270785</v>
       </c>
       <c r="Y4">
-        <v>0.1151828066000099</v>
-      </c>
-      <c r="Z4">
-        <v>3.209458702230192</v>
-      </c>
-      <c r="AA4">
-        <v>0.2015017370839404</v>
+        <v>-0.4387911569532864</v>
       </c>
       <c r="AB4">
-        <v>0.06191801986172708</v>
-      </c>
-      <c r="AC4">
-        <v>0.1395837172222133</v>
+        <v>0.09604425019732928</v>
       </c>
       <c r="AD4">
-        <v>33.1</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>33.1</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AG4">
-        <v>-56.3</v>
+        <v>-71.20700000000001</v>
       </c>
       <c r="AH4">
-        <v>0.007849368019160995</v>
+        <v>0.01307719887532316</v>
       </c>
       <c r="AI4">
-        <v>0.02870025145235412</v>
+        <v>0.01952497675598005</v>
       </c>
       <c r="AJ4">
-        <v>-0.01364021804966687</v>
+        <v>3.766171259321943</v>
       </c>
       <c r="AK4">
-        <v>-0.05291850737851302</v>
+        <v>1.955860136786881</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AN4">
-        <v>0.1482974910394265</v>
+        <v>-0.03609375</v>
+      </c>
+      <c r="AO4">
+        <v>-412.7659574468085</v>
       </c>
       <c r="AP4">
-        <v>-0.2522401433691757</v>
+        <v>3.708697916666667</v>
+      </c>
+      <c r="AQ4">
+        <v>-412.7659574468085</v>
       </c>
     </row>
     <row r="5">
@@ -966,25 +963,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.244</v>
+        <v>0.0974</v>
       </c>
       <c r="G5">
-        <v>-0.1849315068493151</v>
+        <v>-0.2521008403361344</v>
       </c>
       <c r="H5">
-        <v>-0.1849315068493151</v>
+        <v>-0.2521008403361344</v>
       </c>
       <c r="I5">
-        <v>-0.317351598173516</v>
+        <v>-0.1764705882352941</v>
       </c>
       <c r="J5">
-        <v>-0.317351598173516</v>
+        <v>-0.1764705882352941</v>
       </c>
       <c r="K5">
-        <v>-13.1</v>
+        <v>-11.1</v>
       </c>
       <c r="L5">
-        <v>-0.2990867579908676</v>
+        <v>-0.1865546218487395</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,55 +1005,46 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>36.9</v>
+        <v>23.9</v>
       </c>
       <c r="V5">
-        <v>0.2968624296057925</v>
+        <v>0.4345454545454545</v>
       </c>
       <c r="W5">
-        <v>-0.3922155688622754</v>
+        <v>-0.5414634146341464</v>
       </c>
       <c r="X5">
-        <v>0.06210668035617091</v>
+        <v>0.09629375743255376</v>
       </c>
       <c r="Y5">
-        <v>-0.4543222492184463</v>
-      </c>
-      <c r="Z5">
-        <v>2.236405412305336</v>
-      </c>
-      <c r="AA5">
-        <v>-0.7097268317589992</v>
+        <v>-0.6377571720667001</v>
       </c>
       <c r="AB5">
-        <v>0.06192106042955024</v>
-      </c>
-      <c r="AC5">
-        <v>-0.7716478921885495</v>
+        <v>0.09603935114810098</v>
       </c>
       <c r="AD5">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="AG5">
-        <v>-36.3</v>
+        <v>-23.59</v>
       </c>
       <c r="AH5">
-        <v>0.004803843074459568</v>
+        <v>0.005604773097089134</v>
       </c>
       <c r="AI5">
-        <v>0.02843601895734597</v>
+        <v>0.03202479338842975</v>
       </c>
       <c r="AJ5">
-        <v>-0.4125</v>
+        <v>-0.7510347023241006</v>
       </c>
       <c r="AK5">
-        <v>2.29746835443038</v>
+        <v>1.658931082981716</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1065,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-0.04444444444444445</v>
+        <v>-0.0303921568627451</v>
       </c>
       <c r="AP5">
-        <v>2.688888888888889</v>
+        <v>2.312745098039216</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_life.xlsx
@@ -588,115 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>0.112</v>
       </c>
       <c r="E2">
-        <v>0.0312</v>
+        <v>0.171</v>
       </c>
       <c r="G2">
-        <v>0.04614392643884388</v>
+        <v>0.05871507361320023</v>
       </c>
       <c r="H2">
-        <v>0.04614392643884388</v>
+        <v>0.05871507361320023</v>
       </c>
       <c r="I2">
-        <v>0.05113397437694486</v>
+        <v>0.07751264870778067</v>
       </c>
       <c r="J2">
-        <v>0.04886188853165119</v>
+        <v>0.06609516899305715</v>
       </c>
       <c r="K2">
-        <v>152.2</v>
+        <v>288.81</v>
       </c>
       <c r="L2">
-        <v>0.0426677132684814</v>
+        <v>0.06582114043484207</v>
       </c>
       <c r="M2">
-        <v>157.2</v>
+        <v>149.02</v>
       </c>
       <c r="N2">
-        <v>0.02698527139767226</v>
+        <v>0.01712853875242813</v>
       </c>
       <c r="O2">
-        <v>1.032851511169514</v>
+        <v>0.5159793635954434</v>
       </c>
       <c r="P2">
-        <v>143.7</v>
+        <v>144</v>
       </c>
       <c r="Q2">
-        <v>0.02466783396848285</v>
+        <v>0.01655153389041505</v>
       </c>
       <c r="R2">
-        <v>0.9441524310118266</v>
+        <v>0.4985976939856653</v>
       </c>
       <c r="S2">
-        <v>13.5</v>
+        <v>5.02000000000001</v>
       </c>
       <c r="T2">
-        <v>0.08587786259541985</v>
+        <v>0.03368675345591202</v>
       </c>
       <c r="U2">
-        <v>293.3</v>
+        <v>466.3</v>
       </c>
       <c r="V2">
-        <v>0.05034847392453737</v>
+        <v>0.05359708509097597</v>
       </c>
       <c r="W2">
-        <v>-0.3421487603305785</v>
+        <v>0.2504747264671308</v>
       </c>
       <c r="X2">
-        <v>0.09643605904432476</v>
+        <v>0.08278206696819107</v>
       </c>
       <c r="Y2">
-        <v>-0.4385848193749032</v>
+        <v>0.1676926594989397</v>
       </c>
       <c r="Z2">
-        <v>3.437174792830989</v>
+        <v>4.706424970503057</v>
       </c>
       <c r="AB2">
-        <v>0.09604425019732928</v>
+        <v>0.08263581280820602</v>
       </c>
       <c r="AD2">
-        <v>51.003</v>
+        <v>45.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.003</v>
+        <v>45.8</v>
       </c>
       <c r="AG2">
-        <v>-242.297</v>
+        <v>-420.5</v>
       </c>
       <c r="AH2">
-        <v>0.008679289014044815</v>
+        <v>0.005236739500794658</v>
       </c>
       <c r="AI2">
-        <v>0.04246452963308641</v>
+        <v>0.03419696856566863</v>
       </c>
       <c r="AJ2">
-        <v>-0.04339826795242717</v>
+        <v>-0.0507874776559254</v>
       </c>
       <c r="AK2">
-        <v>-0.2669136447107371</v>
+        <v>-0.4816723940435281</v>
       </c>
       <c r="AL2">
-        <v>0.047</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
-        <v>0.047</v>
+        <v>0.01</v>
       </c>
       <c r="AN2">
-        <v>0.2724519230769231</v>
+        <v>0.1326959293060988</v>
       </c>
       <c r="AO2">
-        <v>3880.851063829788</v>
+        <v>34011</v>
       </c>
       <c r="AP2">
-        <v>-1.294321581196581</v>
+        <v>-1.218310879327829</v>
       </c>
       <c r="AQ2">
-        <v>3880.851063829788</v>
+        <v>34011</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bupa Arabia for Cooperative Insurance Company (SASE:8210)</t>
+          <t>Al Sagr Cooperative Insurance Company (SASE:8180)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,115 +716,106 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
-      </c>
-      <c r="E3">
-        <v>0.0312</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
-        <v>0.05862394524104561</v>
+        <v>-0.1483015741507871</v>
       </c>
       <c r="H3">
-        <v>0.05862394524104561</v>
+        <v>-0.1483015741507871</v>
       </c>
       <c r="I3">
-        <v>0.06263645482976338</v>
+        <v>0.05650372825186413</v>
       </c>
       <c r="J3">
-        <v>0.05428689443559332</v>
+        <v>0.04497066183922226</v>
       </c>
       <c r="K3">
-        <v>184</v>
+        <v>5.43</v>
       </c>
       <c r="L3">
-        <v>0.05428689443559332</v>
+        <v>0.04498757249378624</v>
       </c>
       <c r="M3">
-        <v>157.2</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02749164932407618</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8543478260869565</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>143.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02513072524090169</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7809782608695651</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>13.5</v>
-      </c>
-      <c r="T3">
-        <v>0.08587786259541985</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>197.5</v>
+        <v>46.3</v>
       </c>
       <c r="V3">
-        <v>0.03453944492051556</v>
+        <v>0.4873684210526316</v>
       </c>
       <c r="W3">
-        <v>0.1642563827887877</v>
+        <v>0.1560344827586207</v>
       </c>
       <c r="X3">
-        <v>0.09643605904432476</v>
+        <v>0.08278206696819107</v>
       </c>
       <c r="Y3">
-        <v>0.06782032374446295</v>
-      </c>
-      <c r="Z3">
-        <v>3.265947195991521</v>
-      </c>
-      <c r="AA3">
-        <v>0.1772981306610137</v>
+        <v>0.07325241579042963</v>
       </c>
       <c r="AB3">
-        <v>0.09606771152303745</v>
-      </c>
-      <c r="AC3">
-        <v>0.08123041913797624</v>
+        <v>0.08263357694232419</v>
       </c>
       <c r="AD3">
-        <v>50</v>
+        <v>0.394</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>50</v>
+        <v>0.394</v>
       </c>
       <c r="AG3">
-        <v>-147.5</v>
+        <v>-45.906</v>
       </c>
       <c r="AH3">
-        <v>0.008668365666337267</v>
+        <v>0.004130238799085896</v>
       </c>
       <c r="AI3">
-        <v>0.04325633705337831</v>
+        <v>0.007787484681978101</v>
       </c>
       <c r="AJ3">
-        <v>-0.0264782967723405</v>
+        <v>-0.9350633478632826</v>
       </c>
       <c r="AK3">
-        <v>-0.1539023372287145</v>
+        <v>-10.69073125291103</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN3">
-        <v>0.2308402585410896</v>
+        <v>0.05338753387533875</v>
+      </c>
+      <c r="AO3">
+        <v>682</v>
       </c>
       <c r="AP3">
-        <v>-0.6809787626962143</v>
+        <v>-6.220325203252033</v>
+      </c>
+      <c r="AQ3">
+        <v>682</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Sagr Cooperative Insurance Company (SASE:8180)</t>
+          <t>Saudi Enaya Cooperative Insurance Company (SASE:8311)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +835,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.169</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="G4">
-        <v>-0.161590524534687</v>
+        <v>-0.02575757575757576</v>
       </c>
       <c r="H4">
-        <v>-0.161590524534687</v>
+        <v>-0.02575757575757576</v>
       </c>
       <c r="I4">
-        <v>-0.1641285956006768</v>
+        <v>0.0962809917355372</v>
       </c>
       <c r="J4">
-        <v>-0.1641285956006768</v>
+        <v>0.08793388429752066</v>
       </c>
       <c r="K4">
-        <v>-20.7</v>
+        <v>6.38</v>
       </c>
       <c r="L4">
-        <v>-0.1751269035532995</v>
+        <v>0.08787878787878789</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,7 +862,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,70 +871,64 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>71.90000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="V4">
-        <v>1.374760994263863</v>
+        <v>0.4404145077720207</v>
       </c>
       <c r="W4">
-        <v>-0.3421487603305785</v>
+        <v>0.680896478121665</v>
       </c>
       <c r="X4">
-        <v>0.09664239662270785</v>
+        <v>0.08267514338707513</v>
       </c>
       <c r="Y4">
-        <v>-0.4387911569532864</v>
+        <v>0.5982213347345898</v>
       </c>
       <c r="AB4">
-        <v>0.09604425019732928</v>
+        <v>0.08263581280820602</v>
       </c>
       <c r="AD4">
-        <v>0.6929999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.6929999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="AG4">
-        <v>-71.20700000000001</v>
+        <v>-42.394</v>
       </c>
       <c r="AH4">
-        <v>0.01307719887532316</v>
+        <v>0.001097240337039107</v>
       </c>
       <c r="AI4">
-        <v>0.01952497675598005</v>
+        <v>0.00209461328696202</v>
       </c>
       <c r="AJ4">
-        <v>3.766171259321943</v>
+        <v>-0.7835360218829704</v>
       </c>
       <c r="AK4">
-        <v>1.955860136786881</v>
+        <v>-5.229953121144829</v>
       </c>
       <c r="AL4">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0.03609375</v>
-      </c>
-      <c r="AO4">
-        <v>-412.7659574468085</v>
+        <v>0.01458046767537827</v>
       </c>
       <c r="AP4">
-        <v>3.708697916666667</v>
-      </c>
-      <c r="AQ4">
-        <v>-412.7659574468085</v>
+        <v>-5.831361760660248</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saudi Enaya Cooperative Insurance Company (SASE:8311)</t>
+          <t>Bupa Arabia for Cooperative Insurance Company (SASE:8210)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,88 +948,103 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0974</v>
+        <v>0.141</v>
+      </c>
+      <c r="E5">
+        <v>0.171</v>
       </c>
       <c r="G5">
-        <v>-0.2521008403361344</v>
+        <v>0.0661342233877697</v>
       </c>
       <c r="H5">
-        <v>-0.2521008403361344</v>
+        <v>0.0661342233877697</v>
       </c>
       <c r="I5">
-        <v>-0.1764705882352941</v>
+        <v>0.07779234712123019</v>
       </c>
       <c r="J5">
-        <v>-0.1764705882352941</v>
+        <v>0.06603886041244487</v>
       </c>
       <c r="K5">
-        <v>-11.1</v>
+        <v>277</v>
       </c>
       <c r="L5">
-        <v>-0.1865546218487395</v>
+        <v>0.06603886041244487</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>149.02</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.01751404461368498</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.5379783393501806</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>144</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01692405331076793</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.51985559566787</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5.02000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.03368675345591202</v>
       </c>
       <c r="U5">
-        <v>23.9</v>
+        <v>377.5</v>
       </c>
       <c r="V5">
-        <v>0.4345454545454545</v>
+        <v>0.04436687586677009</v>
       </c>
       <c r="W5">
-        <v>-0.5414634146341464</v>
+        <v>0.2504747264671308</v>
       </c>
       <c r="X5">
-        <v>0.09629375743255376</v>
+        <v>0.08282333149126993</v>
       </c>
       <c r="Y5">
-        <v>-0.6377571720667001</v>
+        <v>0.1676513949758609</v>
+      </c>
+      <c r="Z5">
+        <v>4.49908827630591</v>
+      </c>
+      <c r="AA5">
+        <v>0.2971146626622332</v>
       </c>
       <c r="AB5">
-        <v>0.09603935114810098</v>
+        <v>0.08264402534795091</v>
+      </c>
+      <c r="AC5">
+        <v>0.2144706373142823</v>
       </c>
       <c r="AD5">
-        <v>0.31</v>
+        <v>45.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.31</v>
+        <v>45.3</v>
       </c>
       <c r="AG5">
-        <v>-23.59</v>
+        <v>-332.2</v>
       </c>
       <c r="AH5">
-        <v>0.005604773097089134</v>
+        <v>0.00529582997229334</v>
       </c>
       <c r="AI5">
-        <v>0.03202479338842975</v>
+        <v>0.03658832081415071</v>
       </c>
       <c r="AJ5">
-        <v>-0.7510347023241006</v>
+        <v>-0.04062912773347683</v>
       </c>
       <c r="AK5">
-        <v>1.658931082981716</v>
+        <v>-0.3860097606321172</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-0.0303921568627451</v>
+        <v>0.1370650529500756</v>
       </c>
       <c r="AP5">
-        <v>2.312745098039216</v>
+        <v>-1.005143721633888</v>
       </c>
     </row>
   </sheetData>
